--- a/data/trans_dic/P3A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tareas del hogar realizadas por el/la entrevistado/a</t>
+          <t>Tareas del hogar realizadas por el/la entrevistado/a (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,98; 42,43</t>
+          <t>26,22; 42,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,65; 45,23</t>
+          <t>29,48; 44,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,58; 32,53</t>
+          <t>18,0; 31,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82,1; 94,17</t>
+          <t>82,18; 94,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,39; 44,95</t>
+          <t>28,88; 44,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,06; 38,37</t>
+          <t>23,54; 38,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,06; 33,46</t>
+          <t>18,71; 33,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>75,73; 89,81</t>
+          <t>75,59; 90,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,37; 41,58</t>
+          <t>28,6; 40,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29,03; 39,0</t>
+          <t>28,34; 39,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,27; 30,31</t>
+          <t>20,58; 30,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,39; 90,84</t>
+          <t>81,17; 90,75</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,11; 41,29</t>
+          <t>30,94; 41,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,22; 40,01</t>
+          <t>28,25; 40,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,8; 34,57</t>
+          <t>23,58; 34,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77,26; 87,64</t>
+          <t>77,34; 87,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,11; 38,8</t>
+          <t>27,68; 38,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,32; 36,49</t>
+          <t>24,91; 36,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,86; 39,72</t>
+          <t>29,29; 39,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>85,02; 93,17</t>
+          <t>84,77; 93,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,76; 38,56</t>
+          <t>30,63; 38,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,53; 35,98</t>
+          <t>27,82; 36,36</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27,81; 35,72</t>
+          <t>28,59; 36,34</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>82,72; 89,28</t>
+          <t>82,75; 89,45</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,7; 51,77</t>
+          <t>33,66; 51,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,55; 43,33</t>
+          <t>27,21; 43,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,44; 44,87</t>
+          <t>30,8; 44,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84,4; 92,7</t>
+          <t>84,26; 92,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,97; 45,4</t>
+          <t>30,13; 45,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,13; 39,84</t>
+          <t>24,93; 39,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,55; 42,28</t>
+          <t>28,41; 42,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>77,8; 87,39</t>
+          <t>77,34; 87,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>33,61; 45,4</t>
+          <t>34,03; 45,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,12; 38,8</t>
+          <t>27,36; 39,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31,99; 41,18</t>
+          <t>31,73; 41,53</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>82,06; 88,85</t>
+          <t>82,44; 88,7</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,29; 38,23</t>
+          <t>26,06; 37,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,82; 40,11</t>
+          <t>25,14; 39,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,84; 45,62</t>
+          <t>30,75; 45,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78,08; 89,54</t>
+          <t>78,39; 89,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,44; 44,21</t>
+          <t>31,18; 44,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,78; 49,45</t>
+          <t>36,17; 50,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,09; 42,4</t>
+          <t>27,51; 41,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>82,61; 90,38</t>
+          <t>82,65; 89,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,42; 39,48</t>
+          <t>30,47; 39,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,0; 43,13</t>
+          <t>33,03; 43,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>31,2; 40,96</t>
+          <t>30,82; 41,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,32; 89,17</t>
+          <t>81,62; 88,62</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,87; 38,82</t>
+          <t>31,95; 38,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,84; 37,98</t>
+          <t>30,61; 37,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,1; 35,95</t>
+          <t>29,07; 35,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82,54; 88,56</t>
+          <t>82,32; 88,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,55; 39,17</t>
+          <t>32,64; 39,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,1; 37,21</t>
+          <t>30,38; 37,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,84; 36,52</t>
+          <t>30,09; 36,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>83,58; 88,14</t>
+          <t>83,7; 88,48</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,33; 37,99</t>
+          <t>33,34; 38,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31,71; 36,52</t>
+          <t>31,76; 36,45</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,41; 35,26</t>
+          <t>30,42; 35,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>83,9; 87,61</t>
+          <t>83,95; 87,82</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tareas del hogar realizadas por el/la entrevistado/a (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>26580</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>38564</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25496</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>51300</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>32010</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>34383</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>25383</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>51550</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>58590</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>72946</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>50879</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>102849</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>20600; 33385</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>30694; 46305</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18492; 32842</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>47262; 54479</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>25547; 39058</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>26374; 43678</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>18385; 32712</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>46445; 55773</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>47768; 67503</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>61262; 84620</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>41351; 60946</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>96550; 107947</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>66416</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>53984</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>45539</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>131973</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>62564</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>58228</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>72289</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>163488</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>128980</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>112212</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>117828</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>295461</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>57932; 78368</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45008; 64212</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36850; 53888</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>123204; 140008</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>52236; 73041</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>48126; 69754</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>61678; 84098</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>154747; 169876</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>115154; 143556</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>98093; 128193</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>104877; 133325</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>282893; 305800</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>36565</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33645</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>53994</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>154935</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>38471</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>33037</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46510</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>176172</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>75036</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>66683</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>100504</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>331107</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>29111; 44613</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>26659; 42480</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>44446; 63916</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>146526; 160606</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>31112; 46970</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>25386; 40663</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>37549; 56150</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>164332; 185200</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>64577; 86058</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>54654; 78295</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>87739; 114810</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>318545; 342699</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>48477</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>37741</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>45955</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>233358</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>55639</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>56217</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>44751</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>265405</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>104116</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>93958</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>90706</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>498762</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>39369; 56885</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>29040; 45910</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>37547; 56042</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>215929; 246666</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>46172; 66312</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>47639; 66236</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>35764; 54576</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>252496; 274672</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>91152; 118390</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>81654; 106406</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>77689; 103392</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>474186; 514800</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1655</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>178038</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>163934</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>170985</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>571565</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>188683</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>181865</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>188932</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>656615</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>366721</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>345800</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>359917</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>1228181</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>160825; 194731</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>146023; 180617</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>152738; 189092</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>548406; 588993</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>172522; 206363</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>163677; 200904</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>171826; 209631</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>637741; 674181</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>344083; 397200</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>322566; 370197</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>333531; 387098</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1198846; 1254226</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P3A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Edad-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,22; 42,5</t>
+          <t>25,71; 42,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,48; 44,47</t>
+          <t>29,48; 45,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,0; 31,98</t>
+          <t>18,01; 32,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82,18; 94,73</t>
+          <t>82,06; 94,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,88; 44,15</t>
+          <t>28,12; 44,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,54; 38,98</t>
+          <t>23,59; 37,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,71; 33,29</t>
+          <t>19,69; 33,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>75,59; 90,77</t>
+          <t>74,78; 90,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28,6; 40,42</t>
+          <t>29,15; 40,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,34; 39,15</t>
+          <t>28,79; 39,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,58; 30,33</t>
+          <t>20,74; 31,0</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,17; 90,75</t>
+          <t>81,16; 90,84</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,94; 41,85</t>
+          <t>30,2; 41,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,25; 40,3</t>
+          <t>27,94; 39,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,58; 34,48</t>
+          <t>23,24; 34,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77,34; 87,89</t>
+          <t>76,31; 87,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,68; 38,7</t>
+          <t>27,91; 39,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,91; 36,1</t>
+          <t>24,95; 35,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,29; 39,93</t>
+          <t>28,85; 40,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>84,77; 93,06</t>
+          <t>85,03; 93,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,63; 38,18</t>
+          <t>30,85; 38,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,82; 36,36</t>
+          <t>27,75; 35,93</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,59; 36,34</t>
+          <t>28,26; 36,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>82,75; 89,45</t>
+          <t>82,73; 89,5</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,66; 51,59</t>
+          <t>33,81; 51,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27,21; 43,36</t>
+          <t>26,18; 42,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30,8; 44,29</t>
+          <t>31,1; 44,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84,26; 92,36</t>
+          <t>83,94; 92,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,13; 45,49</t>
+          <t>30,37; 45,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,93; 39,94</t>
+          <t>24,89; 39,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,41; 42,48</t>
+          <t>28,81; 42,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>77,34; 87,16</t>
+          <t>77,21; 87,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,03; 45,36</t>
+          <t>34,04; 45,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,36; 39,19</t>
+          <t>28,23; 39,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>31,73; 41,53</t>
+          <t>32,04; 41,13</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>82,44; 88,7</t>
+          <t>82,11; 88,7</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,06; 37,65</t>
+          <t>26,33; 38,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,14; 39,74</t>
+          <t>25,66; 39,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,75; 45,9</t>
+          <t>30,0; 45,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78,39; 89,55</t>
+          <t>78,74; 90,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,18; 44,78</t>
+          <t>31,26; 44,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,17; 50,29</t>
+          <t>35,56; 49,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,51; 41,98</t>
+          <t>27,77; 42,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>82,65; 89,91</t>
+          <t>82,69; 90,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,47; 39,57</t>
+          <t>30,57; 39,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33,03; 43,04</t>
+          <t>32,93; 43,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,82; 41,01</t>
+          <t>30,99; 41,18</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81,62; 88,62</t>
+          <t>82,09; 88,93</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,95; 38,69</t>
+          <t>32,07; 38,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>30,61; 37,87</t>
+          <t>31,15; 38,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,07; 35,99</t>
+          <t>29,41; 36,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82,32; 88,42</t>
+          <t>82,55; 88,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,64; 39,04</t>
+          <t>32,32; 39,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,38; 37,29</t>
+          <t>30,72; 37,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,09; 36,71</t>
+          <t>29,98; 36,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>83,7; 88,48</t>
+          <t>83,6; 88,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,34; 38,49</t>
+          <t>33,31; 37,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31,76; 36,45</t>
+          <t>31,8; 36,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,42; 35,31</t>
+          <t>30,49; 34,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>83,95; 87,82</t>
+          <t>84,1; 87,7</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20600; 33385</t>
+          <t>20200; 33453</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30694; 46305</t>
+          <t>30699; 47430</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18492; 32842</t>
+          <t>18498; 33081</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47262; 54479</t>
+          <t>47192; 54472</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25547; 39058</t>
+          <t>24876; 39621</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26374; 43678</t>
+          <t>26430; 42187</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18385; 32712</t>
+          <t>19350; 33387</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>46445; 55773</t>
+          <t>45947; 55527</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47768; 67503</t>
+          <t>48687; 67580</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61262; 84620</t>
+          <t>62229; 84441</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41351; 60946</t>
+          <t>41677; 62308</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>96550; 107947</t>
+          <t>96547; 108064</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57932; 78368</t>
+          <t>56552; 77586</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45008; 64212</t>
+          <t>44529; 63495</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36850; 53888</t>
+          <t>36311; 54033</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>123204; 140008</t>
+          <t>121559; 139216</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52236; 73041</t>
+          <t>52669; 73831</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48126; 69754</t>
+          <t>48217; 69008</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61678; 84098</t>
+          <t>60750; 84284</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>154747; 169876</t>
+          <t>155217; 170198</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>115154; 143556</t>
+          <t>116004; 143103</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>98093; 128193</t>
+          <t>97840; 126664</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>104877; 133325</t>
+          <t>103675; 133752</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>282893; 305800</t>
+          <t>282825; 305968</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29111; 44613</t>
+          <t>29235; 44232</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26659; 42480</t>
+          <t>25648; 41196</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44446; 63916</t>
+          <t>44885; 64249</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>146526; 160606</t>
+          <t>145957; 161008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31112; 46970</t>
+          <t>31361; 46491</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25386; 40663</t>
+          <t>25336; 40371</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37549; 56150</t>
+          <t>38079; 55671</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>164332; 185200</t>
+          <t>164056; 185576</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64577; 86058</t>
+          <t>64583; 86116</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54654; 78295</t>
+          <t>56401; 78447</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87739; 114810</t>
+          <t>88590; 113705</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>318545; 342699</t>
+          <t>317268; 342724</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39369; 56885</t>
+          <t>39773; 57922</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29040; 45910</t>
+          <t>29646; 45944</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>37547; 56042</t>
+          <t>36626; 55905</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>215929; 246666</t>
+          <t>216897; 248020</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>46172; 66312</t>
+          <t>46289; 65589</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>47639; 66236</t>
+          <t>46828; 64806</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35764; 54576</t>
+          <t>36108; 55007</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>252496; 274672</t>
+          <t>252613; 276247</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>91152; 118390</t>
+          <t>91443; 117192</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81654; 106406</t>
+          <t>81400; 106790</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>77689; 103392</t>
+          <t>78137; 103813</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>474186; 514800</t>
+          <t>476890; 516612</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>160825; 194731</t>
+          <t>161434; 195904</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>146023; 180617</t>
+          <t>148578; 181319</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>152738; 189092</t>
+          <t>154519; 189234</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>548406; 588993</t>
+          <t>549921; 590002</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>172522; 206363</t>
+          <t>170832; 207188</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>163677; 200904</t>
+          <t>165504; 202389</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>171826; 209631</t>
+          <t>171223; 207722</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>637741; 674181</t>
+          <t>637030; 673605</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>344083; 397200</t>
+          <t>343708; 389694</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>322566; 370197</t>
+          <t>323044; 373546</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>333531; 387098</t>
+          <t>334332; 382916</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1198846; 1254226</t>
+          <t>1200986; 1252460</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P3A_R-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>36,18%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>30,69%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>25,83%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>83,07%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>33,83%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>37,04%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>24,82%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>89,2%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>36,18%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>30,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>25,83%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,54%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,71; 42,58</t>
+          <t>28,39; 44,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,48; 45,55</t>
+          <t>24,06; 38,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,01; 32,21</t>
+          <t>19,06; 33,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82,06; 94,72</t>
+          <t>74,52; 89,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,12; 44,79</t>
+          <t>24,98; 42,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,59; 37,65</t>
+          <t>29,65; 45,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,69; 33,98</t>
+          <t>18,58; 32,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>74,78; 90,37</t>
+          <t>83,11; 94,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,15; 40,46</t>
+          <t>29,37; 41,58</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28,79; 39,06</t>
+          <t>29,03; 39,0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20,74; 31,0</t>
+          <t>20,27; 30,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,16; 90,84</t>
+          <t>81,44; 90,7</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>33,15%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>30,14%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>34,33%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>89,28%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>35,47%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>33,88%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>29,14%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>82,85%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>33,15%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>30,14%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>34,33%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,77%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>30,2; 41,44</t>
+          <t>28,11; 38,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,94; 39,85</t>
+          <t>25,32; 36,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,24; 34,58</t>
+          <t>28,86; 39,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76,31; 87,39</t>
+          <t>84,01; 92,81</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,91; 39,12</t>
+          <t>30,11; 41,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,95; 35,71</t>
+          <t>28,22; 40,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,85; 40,02</t>
+          <t>23,8; 34,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>85,03; 93,23</t>
+          <t>78,44; 88,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,85; 38,06</t>
+          <t>30,76; 38,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27,75; 35,93</t>
+          <t>27,53; 35,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,26; 36,46</t>
+          <t>27,81; 35,72</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>82,73; 89,5</t>
+          <t>83,27; 89,55</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>37,26%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>32,45%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>35,19%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>82,33%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>42,28%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>34,34%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>37,41%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>89,1%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>37,26%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>32,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>35,19%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,81; 51,15</t>
+          <t>29,97; 45,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,18; 42,05</t>
+          <t>25,13; 39,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31,1; 44,52</t>
+          <t>28,55; 42,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83,94; 92,59</t>
+          <t>77,22; 86,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,37; 45,02</t>
+          <t>33,7; 51,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,89; 39,65</t>
+          <t>26,55; 43,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,81; 42,12</t>
+          <t>31,44; 44,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>77,21; 87,33</t>
+          <t>83,66; 92,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,04; 45,39</t>
+          <t>33,61; 45,4</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>28,23; 39,26</t>
+          <t>28,12; 38,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32,04; 41,13</t>
+          <t>31,99; 41,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>82,11; 88,7</t>
+          <t>81,55; 88,4</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>37,57%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>42,69%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34,42%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>86,96%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>32,09%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>32,67%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>37,64%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>84,72%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>37,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>42,69%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,42%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,49%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,33; 38,34</t>
+          <t>31,44; 44,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,66; 39,77</t>
+          <t>35,78; 49,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30,0; 45,78</t>
+          <t>27,09; 42,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78,74; 90,04</t>
+          <t>82,86; 90,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,26; 44,29</t>
+          <t>26,29; 38,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,56; 49,21</t>
+          <t>25,82; 40,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,77; 42,31</t>
+          <t>30,84; 45,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>82,69; 90,43</t>
+          <t>81,72; 89,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,57; 39,17</t>
+          <t>30,42; 39,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32,93; 43,2</t>
+          <t>33,0; 43,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,99; 41,18</t>
+          <t>31,2; 40,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,09; 88,93</t>
+          <t>83,6; 89,04</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>35,7%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33,75%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>33,09%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>85,88%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>35,37%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>34,37%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>32,54%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>85,8%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>35,7%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>33,75%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>33,09%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,19%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>32,07; 38,92</t>
+          <t>32,55; 39,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,15; 38,02</t>
+          <t>30,1; 37,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,41; 36,02</t>
+          <t>29,84; 36,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82,55; 88,57</t>
+          <t>83,24; 87,98</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,32; 39,2</t>
+          <t>31,87; 38,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,72; 37,56</t>
+          <t>30,84; 37,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,98; 36,38</t>
+          <t>29,1; 35,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>83,6; 88,4</t>
+          <t>84,06; 88,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33,31; 37,76</t>
+          <t>33,33; 37,99</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31,8; 36,78</t>
+          <t>31,71; 36,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30,49; 34,92</t>
+          <t>30,41; 35,26</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>84,1; 87,7</t>
+          <t>84,51; 87,73</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>97</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32010</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>34383</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>25383</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>41979</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>26580</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>38564</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>25496</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>51300</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>32010</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>34383</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>25383</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>51550</t>
+          <t>46837</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>102849</t>
+          <t>88817</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20200; 33453</t>
+          <t>25111; 39766</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30699; 47430</t>
+          <t>26954; 42989</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18498; 33081</t>
+          <t>18731; 32882</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47192; 54472</t>
+          <t>37662; 45094</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>24876; 39621</t>
+          <t>19623; 33335</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26430; 42187</t>
+          <t>30875; 47091</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19350; 33387</t>
+          <t>19078; 33412</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45947; 55527</t>
+          <t>43291; 49451</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>48687; 67580</t>
+          <t>49047; 69455</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62229; 84441</t>
+          <t>62755; 84302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41677; 62308</t>
+          <t>40739; 60916</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>96547; 108064</t>
+          <t>83577; 93078</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>220</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>62564</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>58228</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>72289</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>140632</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>66416</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>53984</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>45539</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>131973</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>62564</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>58228</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>72289</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>163488</t>
+          <t>122326</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>295461</t>
+          <t>262958</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56552; 77586</t>
+          <t>53044; 73225</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44529; 63495</t>
+          <t>48924; 70509</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36311; 54033</t>
+          <t>60786; 83646</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>121559; 139216</t>
+          <t>132337; 146197</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>52669; 73831</t>
+          <t>56385; 77322</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48217; 69008</t>
+          <t>44959; 63759</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60750; 84284</t>
+          <t>37184; 54026</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>155217; 170198</t>
+          <t>114148; 128631</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>116004; 143103</t>
+          <t>115653; 144983</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>97840; 126664</t>
+          <t>97065; 126865</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>103675; 133752</t>
+          <t>102028; 131038</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>282825; 305968</t>
+          <t>252336; 271371</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>208</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>38471</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33037</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>46510</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>164763</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>36565</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>33645</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>53994</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>154935</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>38471</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>33037</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46510</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>176172</t>
+          <t>155285</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>331107</t>
+          <t>320048</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29235; 44232</t>
+          <t>30947; 46878</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25648; 41196</t>
+          <t>25582; 40559</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44885; 64249</t>
+          <t>37732; 55879</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>145957; 161008</t>
+          <t>154537; 173510</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31361; 46491</t>
+          <t>29145; 44766</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25336; 40371</t>
+          <t>26012; 42459</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38079; 55671</t>
+          <t>45368; 64759</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>164056; 185576</t>
+          <t>146841; 161885</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64583; 86116</t>
+          <t>63771; 86151</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56401; 78447</t>
+          <t>56177; 77528</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>88590; 113705</t>
+          <t>88435; 113845</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>317268; 342724</t>
+          <t>306351; 332073</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>291</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>55639</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>56217</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>44751</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>254492</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>48477</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>37741</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>45955</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>233358</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>55639</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>56217</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>44751</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>265405</t>
+          <t>220501</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>498762</t>
+          <t>474993</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39773; 57922</t>
+          <t>46556; 65467</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29646; 45944</t>
+          <t>47125; 65122</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>36626; 55905</t>
+          <t>35219; 55125</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>216897; 248020</t>
+          <t>242496; 264683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>46289; 65589</t>
+          <t>39712; 57752</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>46828; 64806</t>
+          <t>29831; 46341</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36108; 55007</t>
+          <t>37656; 55710</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>252613; 276247</t>
+          <t>209660; 229383</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>91443; 117192</t>
+          <t>91013; 118108</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>81400; 106790</t>
+          <t>81576; 106615</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>78137; 103813</t>
+          <t>78656; 103259</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>476890; 516612</t>
+          <t>459147; 488989</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>237</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>253</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>816</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>839</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>188683</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>181865</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>188932</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>601865</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>178038</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>163934</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>170985</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>571565</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>188683</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>181865</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>188932</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>656615</t>
+          <t>544949</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1228181</t>
+          <t>1146816</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>161434; 195904</t>
+          <t>172022; 207056</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>148578; 181319</t>
+          <t>162166; 200479</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>154519; 189234</t>
+          <t>170425; 208535</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>549921; 590002</t>
+          <t>583378; 616585</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>170832; 207188</t>
+          <t>160422; 195426</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>165504; 202389</t>
+          <t>147102; 181161</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>171223; 207722</t>
+          <t>152883; 188892</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>637030; 673605</t>
+          <t>529290; 559406</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>343708; 389694</t>
+          <t>343940; 392042</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>323044; 373546</t>
+          <t>322120; 370964</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>334332; 382916</t>
+          <t>333384; 386607</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1200986; 1252460</t>
+          <t>1124354; 1167240</t>
         </is>
       </c>
     </row>
